--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-05_attendance_records_打刻記録_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-05_attendance_records_打刻記録_テーブル詳細設計書.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C22"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -576,6 +578,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -644,7 +648,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -684,12 +688,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち attendance_records を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
-章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
+          <t>本書の位置づけ：KF-DD-003 は全 10 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち attendance_records を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration の V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql（Flyway。KF-DD-003 v2.3 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）に、2026/10/05 のコード（AttendanceService / RequestService / ApprovalService / DepartmentController）から起こした ONL-024〜026（休憩・離席の開始・終了、部署一覧。番号は仮）と既存処理の追加アクセスを重ね、BAT-001〜003 と合わせて抽出した。
+章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications / attendance_breaks）のみ作成している。</t>
         </is>
       </c>
     </row>
@@ -712,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -723,6 +729,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -799,15 +806,15 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="48.5" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>バックアップ（BAT-003）</t>
+          <t>休憩・離席の子表</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>区間は attendance_breaks（KF-DD-TBL-10）。バックアップ・アーカイブ・復元は親子セットで扱う（復元は親 → 子の順）。work_minutes を手動で直す場合は、子表の区間（4.4 の規則）に合わせる。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -815,15 +822,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>マイグレーション</t>
+          <t>バックアップ（BAT-003）</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -831,79 +838,64 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="48.5" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>マイグレーション</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Flyway（V1__init_schema.sql：set_updated_at 関数・トリガ・初期データを含む／V2・V3：祝日の初期データ／V4：attendance_breaks の追加／V5：requests への休憩・離席修正の 3 列と制約の追加）＋ spring.jpa.hibernate.ddl-auto=validate。V1〜V5 は適用後に編集せず、列追加・索引追加は次の版 V6__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.2 既知課題・未決事項（未解決のもの。解消済みは 9.2b）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>推奨対応</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="77.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
@@ -971,7 +963,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -984,7 +976,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1003,324 +995,362 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48.5" customHeight="1">
+    <row r="16" ht="106.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>C-7</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>保存期間 5 年を超えたデータの自動削除・アーカイブが未実装</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §9（決定 6）は勤怠・申請・監査ログの保存期間を 5 年（設定値）とし、BAT-005『監査ログ／履歴の保存期間管理（アーカイブ）』を計画している。現行の backend には削除・アーカイブ処理も保存期間の設定値も無く、業務データは物理削除しない（例外は通知・祝日・再提出時の承認ステップ）。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始から 5 年間は影響しない。5 年を超えた後の扱い（残す／消す・退避）の手順が無く、運用者の判断になる。件数は 5 年で 5 表合計（attendance_breaks 約 75 万行を含む）約 120 万行規模で、容量・性能上の問題にはなりにくい。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始（2026 年）の 5 年後（2031 年）までに、BAT-005 の設計・実装、または手動の退避 SQL の手順を決める。それまでは『消さずに保持する』方針で運用する（5 年はこの方針の目安）。</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48.5" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>A-2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>勤怠値の整合 CHECK が無い</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>clock_out &gt;= clock_in、work_minutes &gt;= 0、overtime_minutes &gt;= 0、clock_out があれば clock_in も必須、を DB が保証しない。</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>打刻修正（ONL-010）や手動更新で退勤が出勤より前、負の時間などを保存できる。</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>CHECK を追加（ck_att_time, ck_att_minutes）。</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="77.5" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18" ht="135.5" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>A-3</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>日跨ぎ勤務・休憩・修正履歴に非対応</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・所定労働時間の列が無く work_minutes の計算規則はアプリ内。ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠が DB に無い。</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>break_minutes 列、attendance_record_audits（修正履歴）の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>日跨ぎ勤務・修正履歴に非対応（休憩・離席は V4 で対応済み）</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・離席は V4 の子表 attendance_breaks に区間として記録し、work_minutes は区間を反映して計算するようになった（休憩列・離席列は不要）。所定労働時間の列は無く（480 分はアプリ内の定数）、ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。休憩・離席修正（BREAK_CORRECTION）の反映も、区間の修正前の値を残さない。</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠は子表の区間と AttendanceCalculator の規則（KF-DD-TBL-10 の 4.4）で、DB は結果の分だけを保持する。</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>attendance_record_audits（修正履歴）の追加を検討。</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="77.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="77.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>月次集計は work_date 先頭の索引が無い</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>ONL-018/020 の集計サブクエリは work_date BETWEEN のみで user_id を限定しない。idx は user_id 先頭のため使えず、期間で全件走査になる（300 名×約 22 日≒6,600 行/月、年 75,000 行までは問題なし）。</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>数年分（数十万行）に増えると月次集計が遅くなる。</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>必要になった時点で idx_att_work_date (work_date) を追加（現状は不要）。</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="20" ht="106.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>BR-4</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>退勤済み・過去日に継続中の区間が残りうる</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>退勤打刻（ONL-003）は継続中の区間があると E-022 で拒否するが、打刻修正申請の承認（ONL-010 の applyClockCorrection）は継続中の区間を確認せずに clock_out を設定する。また終了を押し忘れたまま日が替わると、過去日の継続中の区間が残る（開始・終了の打刻は本日の行だけが対象）。継続中の区間は勤務時間の計算では無視される。</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>ONL-004 の応答に endAt が null の区間が残る。勤務時間に反映されない（休憩・離席が控除されない）。</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>打刻修正の承認時に継続中の区間を検出して拒否または終了させる。当面は休憩・離席修正申請（同種別の継続中の区間を修正できる）で補う。10章の確認 SQL で検出。</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="106.5" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24" ht="106.5" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>V1 の全 9 表（V4 の attendance_breaks にも同様）に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="92" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="25" ht="135.5" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="48.5" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26" ht="135.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>A-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>idx_att_user_date が uq_attendance_records_1 と同一列で冗長</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>idx_att_user_date を削除（uq_attendance_records_1 が同じ検索を担う）。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>attendance_records</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>ONL-002</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>INACTIVE にされたユーザーでも、発行済みトークンの有効期限（8時間）内は打刻できる（トークン失効は未対応。ONL-001 と同じ制約）。updated_at は UPDATE 時に DB トリガ（set_updated_at）が自動更新する（アプリは設定しない）。</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>ONL-003</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>日跨ぎ勤務（深夜0時を越える勤務）は未対応。前日出勤・未退勤の行は翌日の退勤打刻では更新されず E-007（打刻修正申請で補正）。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
-        </is>
-      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>ONL-004</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>未対応・制約</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>暦日の空白埋め・休日／休暇種別の表示は行わない。不正な month は Service の検証で E-002 を返す。他の API の型変換エラー（パス変数・クエリ型不一致）は ONL-001 の handleTypeMismatch が E-002 / 400 にする。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -1330,40 +1360,143 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（今後）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+          <t>INACTIVE にされたユーザーでも、発行済みトークンの有効期限（2時間）内は打刻できる（トークン失効は未対応。ONL-001 と同じ制約）。updated_at は UPDATE 時に DB トリガ（set_updated_at）が自動更新する（アプリは設定しない）。</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
     </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>ONL-003</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>日跨ぎ勤務（深夜0時を越える勤務）は未対応。前日出勤・未退勤の行は翌日の退勤打刻では更新されず E-007（打刻修正申請で補正）。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>ONL-004</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>未対応・制約</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>暦日の空白埋め・休日／休暇種別の表示は行わない。不正な month は Service の検証で E-002 を返す。他の API の型変換エラー（パス変数・クエリ型不一致）は ONL-001 の handleTypeMismatch が E-002 / 400 にする。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（今後）</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="48.5" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1377,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1388,6 +1521,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1592,7 +1726,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="106.5" customHeight="1">
+    <row r="11" ht="237" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>8</t>
@@ -1600,17 +1734,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>勤務時間の再計算差（拘束時間 − 休憩［6h超45分/8h超60分］と work_minutes）</t>
+          <t>勤務時間の再計算差（拘束 − 離席 − 休憩［打刻があれば打刻合計・無ければ 6h超45分/8h超60分］と work_minutes）</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>WITH g AS (SELECT id, work_minutes, overtime_minutes, (EXTRACT(EPOCH FROM clock_out - clock_in)/60)::int AS gross FROM attendance_records WHERE clock_out IS NOT NULL AND clock_in IS NOT NULL) SELECT id, work_minutes, gross - CASE WHEN gross &gt; 480 THEN 60 WHEN gross &gt; 360 THEN 45 ELSE 0 END AS calc_work FROM g WHERE work_minutes &lt;&gt; gross - CASE WHEN gross &gt; 480 THEN 60 WHEN gross &gt; 360 THEN 45 ELSE 0 END OR overtime_minutes &lt;&gt; GREATEST(work_minutes - 480, 0);</t>
+          <t>WITH b AS (SELECT attendance_record_id AS rid, COALESCE(SUM((EXTRACT(EPOCH FROM date_trunc('minute', end_at) - date_trunc('minute', start_at))/60)::int) FILTER (WHERE kind = 'BREAK' AND end_at IS NOT NULL), 0) AS brk, COALESCE(SUM((EXTRACT(EPOCH FROM date_trunc('minute', end_at) - date_trunc('minute', start_at))/60)::int) FILTER (WHERE kind = 'AWAY' AND end_at IS NOT NULL), 0) AS away FROM attendance_breaks GROUP BY 1), g AS (SELECT a.id, a.work_minutes, a.overtime_minutes, (EXTRACT(EPOCH FROM date_trunc('minute', a.clock_out) - date_trunc('minute', a.clock_in))/60)::int AS gross, COALESCE(b.brk, 0) AS brk, COALESCE(b.away, 0) AS away FROM attendance_records a LEFT JOIN b ON b.rid = a.id WHERE a.clock_out IS NOT NULL AND a.clock_in IS NOT NULL), c AS (SELECT id, work_minutes, overtime_minutes, GREATEST(0, gross - away - CASE WHEN brk &gt; 0 THEN brk WHEN gross - away &gt; 480 THEN 60 WHEN gross - away &gt; 360 THEN 45 ELSE 0 END) AS calc_work FROM g) SELECT id, work_minutes, calc_work FROM c WHERE work_minutes &lt;&gt; calc_work OR overtime_minutes &lt;&gt; GREATEST(calc_work - 480, 0);</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0 行（打刻修正反映後も AttendanceCalculator と一致するはず）</t>
+          <t>0 行（退勤・打刻修正・休憩離席修正の反映後も AttendanceCalculator と一致するはず。出勤〜退勤の範囲外にはみ出す区間がある日は差が出うる。TBL-10 の 10 章参照）</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -1643,7 +1777,7 @@
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1〜V5 のマイグレーション（V1 は v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -1679,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1716,7 +1850,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1">
+    <row r="2" ht="68" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1738,6 +1872,52 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2 追加に伴いデータ例の前提を更新。保存期間 5 年の自動削除・アーカイブは未実装であることを課題 C-7 として追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="188" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>コード（V4・V5 マイグレーション、AttendanceService / AttendanceCalculator）と突合して更新。①子表 attendance_breaks（休憩・離席の区間。V4。KF-DD-TBL-10）との関係（親子・行ロックによる直列化）を 1章・5章・7章に追記②work_minutes / overtime_minutes の計算を、休憩・離席の打刻を反映する規則（離席は全て控除、休憩は打刻合計、打刻の無い日は法定休憩を自動控除）に更新し、退勤打刻・打刻修正承認・休憩離席修正承認（退勤済みの日）の再計算を明記③退勤打刻は継続中の休憩・離席があると拒否（E-022）④8章のデータ例（山田 10/01 に休憩 60 分・離席 10 分を打刻→勤務 470 分）と 10章の再計算 SQL を休憩・離席対応に変更⑤課題 A-3 を更新（休憩の記録は V4 で対応済み）。V3〜V5 追加に伴いデータ例の前提を V1〜V5 適用直後に更新。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1752,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F34"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1763,6 +1943,7 @@
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1791,7 +1972,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="63" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>用途</t>
@@ -1799,7 +1980,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>日次の出退勤を 1 ユーザー 1 日 1 行で記録する。出勤打刻（ONL-002）が INSERT、退勤打刻（ONL-003）が UPDATE、打刻修正申請の承認（ONL-010）が上書き反映。月次表示（ONL-004）、月次集計（ONL-018）、部下一覧（ONL-020）の元データ。</t>
+          <t>日次の出退勤を 1 ユーザー 1 日 1 行で記録する。出勤打刻（ONL-002）が INSERT、退勤打刻（ONL-003）が UPDATE、打刻修正申請の承認（ONL-010）が上書き反映。勤務時間・残業時間は、退勤時と各修正の反映時に、子表 attendance_breaks（休憩・離席の区間。V4 で追加。KF-DD-TBL-10）の打刻を反映して計算する。休憩・離席の打刻（ONL-024/025）はこの行を FOR UPDATE でロックして直列化する（この行自体は更新しない）。月次表示（ONL-004）、月次集計（ONL-018）、部下一覧（ONL-020）の元データ。</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -1815,7 +1996,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway のマイグレーション（backend/src/main/resources/db/migration の V1__init_schema.sql）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -1871,7 +2052,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>更新頻度</t>
@@ -1879,7 +2060,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>更新：1 人あたり 1 日 2 回（出勤 INSERT・退勤 UPDATE）。始業・終業時刻に集中。参照：月次表示・集計。</t>
+          <t>更新：1 人あたり 1 日 2 回（出勤 INSERT・退勤 UPDATE）。休憩・離席の打刻のたびに行ロック（FOR UPDATE。行は更新しない）。始業・終業時刻に集中。参照：月次表示・集計。</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1967,6 +2148,7 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -2079,25 +2261,25 @@
       <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="34" customHeight="1">
+    <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>API-010 POST /api/approvals/{id}/approve</t>
+          <t>API-005 POST /api/requests</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>C/R/U</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
@@ -2106,22 +2288,22 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>月次集計取得</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>API-018 GET /api/admin/reports/monthly</t>
+          <t>API-010 POST /api/approvals/{id}/approve</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R/U</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
@@ -2130,17 +2312,17 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>上長の部下一覧</t>
+          <t>月次集計取得</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>API-020 GET /api/manager/subordinates/summary</t>
+          <t>API-018 GET /api/admin/reports/monthly</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -2154,137 +2336,154 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>ONL-020</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>上長の部下一覧</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>API-020 GET /api/manager/subordinates/summary</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>API-022 POST /api/requests/{id}/submit</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>API-024 POST /api/attendance/break-start</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>API-025 POST /api/attendance/break-end</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>KF-BD-003</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>テーブル定義書（基本）</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>論理名・基本項目</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>KF-BD-005</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>コード定義書</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>コード値と状態遷移の基本設計</t>
-        </is>
-      </c>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-001</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>オンライン設計書</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>ONL-001〜022 の概要</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -2294,17 +2493,17 @@
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2314,17 +2513,17 @@
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2334,55 +2533,139 @@
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="10" t="n"/>
     </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>KF-DD-001</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>オンライン設計書</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ONL-001〜022 の概要（ONL-023 以降は個別のオンライン詳細設計書）</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>KF-DD-ONL-xxx</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>オンライン詳細設計書</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>KF-DD-004 / BAT</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>バッチ設計書</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>BAT-001〜003 の使用</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="106.5" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元（V2・V3 は祝日の初期データのみ）</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="35">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C38:F38"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="C35:F35"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C27:F27"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2397,7 +2680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2415,10 +2698,11 @@
     <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（db/migration の V1・V4・V5 から自動生成。物理列順）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2559,7 +2843,7 @@
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>使用ONL: 002, 003, 010</t>
+          <t>使用ONL: 002, 003, 010, 024, 025</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2908,7 @@
           <t>旧KF-DD-003: users.id
 fk_attendance_records_user_id: → users.id
 uq_attendance_records_1（複合: user_id, work_date）
-使用ONL: 002, 003, 004, 010, 018, 020</t>
+使用ONL: 002, 003, 004, 010, 018, 020, 024, 025</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2972,7 @@
         <is>
           <t>旧KF-DD-003: (user_id, work_date)で一意
 uq_attendance_records_1（複合: user_id, work_date）
-使用ONL: 002, 003, 004, 010, 018, 020</t>
+使用ONL: 002, 003, 004, 010, 018, 020, 024, 025</t>
         </is>
       </c>
     </row>
@@ -2746,11 +3030,11 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>使用ONL: 002, 003, 004, 018, 020</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48.5" customHeight="1">
+          <t>使用ONL: 002, 003, 004, 018, 020, 024, 025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="77.5" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
@@ -2793,7 +3077,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>退勤打刻（ONL-003）でサーバー時刻を設定。出勤前・二重退勤は拒否。打刻修正承認で上書き。</t>
+          <t>退勤打刻（ONL-003）でサーバー時刻を設定。出勤前・二重退勤・休憩中／離席中は拒否（E-007／E-006／E-022）。打刻修正承認で上書き（その時点の継続中の休憩・離席は確認しない。課題 BR-4）。</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -2804,11 +3088,11 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>使用ONL: 003, 004</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48.5" customHeight="1">
+          <t>使用ONL: 003, 004, 024, 025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
@@ -2846,12 +3130,12 @@
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>勤務時間（分）。拘束時間から休憩（6h超45分・8h超60分）を控除した値。</t>
+          <t>勤務時間（分）。拘束時間から日中離席（全て）と休憩を控除した値。休憩は打刻があればその合計、打刻が無い日は法定休憩（離席を除いた時間が 6h超45分・8h超60分）を自動控除（AttendanceCalculator）。</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>退勤打刻時にサーバーが計算（休憩控除後の分）。打刻修正承認時に再計算。出勤時点では NULL。</t>
+          <t>退勤打刻時にサーバーが計算（休憩・離席の打刻を反映。AttendanceCalculator。KF-DD-TBL-10 の 4.4）。打刻修正承認（ONL-010）と、休憩・離席修正の承認時（退勤済みの日のみ）に再計算。出勤時点では NULL。</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -2909,7 +3193,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>退勤打刻時に計算（0 以上）。出勤時点では NULL。</t>
+          <t>work_minutes と同時に計算（勤務時間 − 480 分、0 以上）。出勤時点では NULL。</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -3035,7 +3319,7 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値はマイグレーション（V1・V4・V5）の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -3068,7 +3352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3079,10 +3363,11 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（マイグレーションの定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3287,6 +3572,7 @@
       </c>
       <c r="F9" s="10" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -3365,7 +3651,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="193.5" customHeight="1">
+    <row r="14" ht="382" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>uq_attendance_records_1</t>
@@ -3398,10 +3684,16 @@
 ○ ONL-003 打刻行の検索・行ロック  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?
 ○ ONL-003 退勤の更新  [先頭 2/2 列で絞込]  WHERE id = ?
 ○ ONL-004 月次の打刻記録の検索  [先頭 1/2 列で絞込]  WHERE user_id = ? AND work_date BETWEEN ? AND ?
-○ ONL-010 打刻の取得・反映  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?</t>
-        </is>
-      </c>
-    </row>
+○ ONL-005 休憩・離席修正の検証：対象日の打刻行  [先頭 1/2 列で絞込]  WHERE user_id = ? AND work_date BETWEEN ? AND ?
+○ ONL-010 打刻の取得・反映  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?
+○ ONL-010 【休憩・離席修正】対象日の打刻行の検索・行ロック  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?
+○ ONL-022 休憩・離席修正の再検証：対象日の打刻行  [先頭 1/2 列で絞込]  WHERE user_id = ? AND work_date BETWEEN ? AND ?
+○ ONL-024 打刻行の検索・行ロック  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?
+○ ONL-025 打刻行の検索・行ロック  [先頭 2/2 列で絞込]  WHERE user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -3478,10 +3770,11 @@
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（適用済みのマイグレーションは変更しない。提案のみ。DDL は V1〜V5＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B22" s="9" t="n"/>
@@ -3594,7 +3887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3605,6 +3898,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -3681,6 +3975,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -3725,18 +4020,35 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>なし（独立した表）</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>attendance_record_id</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>0..*</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>fk_attendance_breaks_record</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -3765,6 +4077,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
@@ -3785,7 +4098,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>親：users（user_id、必須）。子：なし。</t>
+          <t>親：users（user_id、必須）。子：attendance_breaks（attendance_record_id、0..*。休憩・離席の区間。V4）。</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -3801,7 +4114,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>打刻修正申請（requests.request_type='CLOCK_CORRECTION'）との FK は無い。承認時に start_date の行へ上書きし、行が無ければ INSERT（ONL-010）。修正前の値は残らない（課題 A-3）。</t>
+          <t>打刻修正申請（requests.request_type='CLOCK_CORRECTION'）との FK は無い。承認時に start_date の行へ上書きし、行が無ければ INSERT（ONL-010）。その日の休憩・離席を考慮して勤務時間を再計算する。修正前の値は残らない（課題 A-3）。</t>
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
@@ -3817,7 +4130,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>整合性をアプリで守る点：(1) 退勤は出勤済み・未退勤の行のみ（E-006/E-007）、(2) work_minutes/overtime_minutes は退勤時にサーバー計算、(3) 日跨ぎ勤務は未対応。</t>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）との FK も無い。最終承認で子表 attendance_breaks に区間を追加・修正し、退勤済みの日だけこの行の work_minutes / overtime_minutes を再計算（UPDATE）する。出勤打刻の無い日は修正できない（E-003）。</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -3825,8 +4138,24 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10" t="n"/>
     </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>整合性 4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>整合性をアプリで守る点：(1) 退勤は出勤済み・未退勤の行のみ（E-006/E-007）で、継続中の休憩・離席が無いこと（E-022）、(2) work_minutes/overtime_minutes は退勤時と修正反映時にサーバー計算（休憩・離席の打刻を反映）、(3) 日跨ぎ勤務は未対応。</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
@@ -3835,6 +4164,7 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3848,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J25"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3863,6 +4193,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -3991,25 +4322,25 @@
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="10" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>C/R/U</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>規格 tables：C/R/U ／ SQL 由来：C/R/U</t>
+          <t>規格 tables：R ／ SQL 由来：R</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -4019,25 +4350,25 @@
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="10" t="n"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>月次集計取得</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C/R/U</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>規格 tables：R ／ SQL 由来：R</t>
+          <t>規格 tables：C/R/U ／ SQL 由来：C/R/U</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -4050,12 +4381,12 @@
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>上長の部下一覧</t>
+          <t>月次集計取得</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -4075,15 +4406,15 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>BAT-003</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>データバックアップ（pg_dump）</t>
+          <t>上長の部下一覧</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -4093,7 +4424,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>BAT 詳細設計書の使用テーブル</t>
+          <t>規格 tables：R ／ SQL 由来：R</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -4103,15 +4434,55 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="10" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>6.2 アクセスパターン詳細（SQL 全文）</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>規格 tables：R ／ SQL 由来：R</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>規格 tables：R ／ SQL 由来：R</t>
+        </is>
+      </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
@@ -4120,375 +4491,252 @@
       <c r="J12" s="10" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>規格 tables：R ／ SQL 由来：R</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>データバックアップ（pg_dump）</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>BAT 詳細設計書の使用テーブル</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="10" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>6.2 アクセスパターン詳細（SQL 全文）</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>SQL 区分（規格のラベル）</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>SQL 全文</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>WHERE 条件</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>ORDER BY</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>想定件数</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>ロック</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>使用索引（○先頭列で絞込／△任意条件）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="63" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>ONL-002</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>出勤打刻</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>user_id = ? AND work_date = ?</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>FOR UPDATE（悲観ロック）</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>○uq_attendance_records_1</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="19" ht="63" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ONL-002</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>出勤打刻</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>新規打刻（saveAndFlush・行なしの場合）</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>INSERT INTO attendance_records (user_id, work_date, clock_in, clock_out, work_minutes, overtime_minutes)
 VALUES (?, ?, ?, NULL, NULL, NULL)</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="12" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>1 件</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>（索引なし／PK 結合）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48.5" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="20" ht="48.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>ONL-002</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>出勤打刻</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>既存行への打刻（saveAndFlush・行ありで clock_in が NULL の場合）</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>UPDATE attendance_records SET user_id = ?, work_date = ?, clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>行ロック（更新行に暗黙で取得）</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>○attendance_records_pkey, ○uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>ONL-003</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>退勤打刻</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>user_id = ? AND work_date = ?</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>FOR UPDATE（悲観ロック）</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>○uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ONL-003</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>退勤打刻</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>退勤の更新（saveAndFlush）</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>UPDATE attendance_records SET user_id = ?, work_date = ?, clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>行ロック（更新行に暗黙で取得）</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>○attendance_records_pkey, ○uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="77.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>ONL-004</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>月次勤怠取得</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>月次の打刻記録の検索（AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc）</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>user_id = ? AND work_date BETWEEN ? AND ?</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>work_date ASC</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>1ユーザー分（日付範囲があれば月31件以内）</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>○uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>承認</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>user_id = ? AND work_date = ?</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr"/>
@@ -4499,68 +4747,72 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>FOR UPDATE（悲観ロック）</t>
+          <t>行ロック（更新行に暗黙で取得）</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>○uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48.5" customHeight="1">
+          <t>○attendance_records_pkey, ○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="63" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-003</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>退勤打刻</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO attendance_records(user_id, work_date, clock_in, clock_out, work_minutes, overtime_minutes) VALUES (?, ?, ?, ?, ?, ?)</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr"/>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
       <c r="G21" s="12" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>1 件</t>
+          <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>FOR UPDATE（悲観ロック）</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>（索引なし／PK 結合）</t>
+          <t>○uq_attendance_records_1</t>
         </is>
       </c>
     </row>
     <row r="22" ht="48.5" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-003</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>退勤打刻</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4570,12 +4822,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+          <t>退勤の更新（saveAndFlush）</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>UPDATE attendance_records SET clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?</t>
+          <t>UPDATE attendance_records SET user_id = ?, work_date = ?, clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -4596,32 +4848,324 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
+          <t>○attendance_records_pkey, ○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="77.5" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>ONL-004</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>月次勤怠取得</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>月次の打刻記録の検索（AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc）</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date BETWEEN ? AND ?</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>work_date ASC</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>1ユーザー分（日付範囲があれば月31件以内）</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>申請作成</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の検証：対象日の打刻行（AttendanceRecordRepository#findByUserIdAndWorkDateBetweenOrderByWorkDateAsc。提出時のみ）</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date BETWEEN ? AND ?</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>work_date ASC</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>1ユーザー分（日付範囲があれば月31件以内）</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO attendance_records(user_id, work_date, clock_in, clock_out, work_minutes, overtime_minutes) VALUES (?, ?, ?, ?, ?, ?)</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>1 件</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>（索引なし／PK 結合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE attendance_records SET clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>行ロック（更新行に暗黙で取得）</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
           <t>○attendance_records_pkey</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="409" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="28" ht="92" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>【休憩・離席修正】対象日の打刻行の検索・行ロック（findWithLockByUserIdAndWorkDate。AttendanceService#applyBreakCorrection）</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="409" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>ONL-018</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>月次集計取得</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>月次集計（ReportRepository#findMonthlySummary。ONL-020 と共用）</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>SELECT u.id,
        u.name,
@@ -4652,54 +5196,54 @@
 ORDER BY CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>全件走査になりうる（表の件数：年75,000）</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>（索引なし／PK 結合）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="409" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="30" ht="409" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>ONL-020</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>上長の部下一覧</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>部下の月次集計（ReportRepository#findMonthlySummary。ONL-018 と同一文。バインド値：departmentId=NULL、managerId=ログイン上長の ID）</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>SELECT u.id,
        u.name,
@@ -4730,60 +5274,212 @@
 ORDER BY CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>全件走査になりうる（表の件数：年75,000）</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>（索引なし／PK 結合）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の再検証：対象日の打刻行（revalidateForSubmit → validateBreakCorrection）</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ? ORDER BY work_date ASC</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date BETWEEN ? AND ?</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>work_date ASC</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>1ユーザー分（日付範囲があれば月31件以内）</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="77.5" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の開始</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate。E-007 / E-006 の判定）</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48.5" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の終了</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>打刻行の検索・行ロック（findWithLockByUserIdAndWorkDate）</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND work_date = ?</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>○uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>※ 想定件数・使用索引はクエリ条件から機械的に推定した目安。Hibernate が発行する SQL は列を全て列挙する（SELECT * と表記）。BAT-003 は pg_dump（COPY）による全件読取のためこの表では省略。</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="10" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="15">
+    <mergeCell ref="D14:J14"/>
     <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D9:J9"/>
     <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="D12:J12"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="D13:J13"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="D5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4798,7 +5494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4809,6 +5505,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -4829,7 +5526,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>SELECT * FROM attendance_records WHERE user_id=? AND work_date=? FOR UPDATE（findWithLockByUserIdAndWorkDate）。ONL-002/003/010。行が無いときは何もロックされない点に注意 → INSERT 競合は UNIQUE が最終防衛。</t>
+          <t>SELECT * FROM attendance_records WHERE user_id=? AND work_date=? FOR UPDATE（findWithLockByUserIdAndWorkDate）。ONL-002/003/010 と、休憩・離席の開始・終了（ONL-024/025）、休憩・離席修正の承認（ONL-010）。行が無いときは何もロックされない点に注意 → INSERT 競合は UNIQUE が最終防衛。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -4869,7 +5566,7 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10" t="n"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ロック順序</t>
@@ -4877,7 +5574,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>requests → attendance_records（ONL-010）。打刻（ONL-002/003）は attendance_records 単独。</t>
+          <t>requests → attendance_records → attendance_breaks（ONL-010）。打刻（ONL-002/003）は attendance_records 単独（ONL-003 は子表の継続中区間を読むだけ）。休憩・離席の打刻（ONL-024/025）は attendance_records（FOR UPDATE）→ attendance_breaks。</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -4885,15 +5582,15 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>トランザクション注意</t>
+          <t>休憩・離席の打刻との直列化</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>行ロック付き検索〜saveAndFlush を 1 トランザクションで行う（AttendanceService に @Transactional）。UNIQUE 違反は flush 時に発生するため saveAndFlush を使う。</t>
+          <t>同一ユーザーの出勤・退勤・休憩開始・休憩終了は、この行の FOR UPDATE で直列化される。退勤（ONL-003）は行ロック後に継続中の区間を確認するため、休憩開始と退勤が競合しても『継続中のまま退勤』にはならない（後着は E-022 または E-006）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -4901,61 +5598,54 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>トランザクション注意</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>行ロック付き検索〜saveAndFlush を 1 トランザクションで行う（AttendanceService に @Transactional）。UNIQUE 違反は flush 時に発生するため saveAndFlush を使う。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>7.2 FOR UPDATE を使う処理（アクセスパターンから自動抽出）</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>処理名</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SQL 区分</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="48.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ONL-002</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>出勤打刻</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>処理名</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>SQL 区分</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -4964,12 +5654,12 @@
     <row r="12" ht="48.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>ONL-003</t>
+          <t>ONL-002</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>退勤打刻</t>
+          <t>出勤打刻</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -4985,20 +5675,20 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="48.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-003</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>退勤打刻</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -5009,83 +5699,184 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>7.3 共通前提</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>打刻の取得・反映（AttendanceRecordRepository）</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>【休憩・離席修正】対象日の打刻行の検索・行ロック（findWithLockByUserIdAndWorkDate。AttendanceService#applyBreakCorrection）</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>分離レベル</t>
+    <row r="16" ht="48.5" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
+          <t>休憩・離席の開始</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate。E-007 / E-006 の判定）</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>ロック順序（デッドロック防止）</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+          <t>休憩・離席の終了</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>打刻行の検索・行ロック（findWithLockByUserIdAndWorkDate）</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="10" t="n"/>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>7.3 共通前提</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>分離レベル</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ロック順序（デッドロック防止）</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>users → requests → approval_steps → leave_balances / attendance_records → attendance_breaks → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一。休憩・離席の打刻 ONL-024/025 は attendance_records の行ロック → attendance_breaks）。</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>ロック待ち</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>バッチは lock.timeout=5000ms（BAT-001 D-8）。オンラインは既定（待ち続ける）のためトランザクションを短く保つ。</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="19">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5099,7 +5890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5115,6 +5906,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -5140,8 +5932,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>山田 太郎の勤怠例（9:00〜18:00（拘束540分・休憩60分）→ work_minutes=480、残業 0／翌日 9:05〜20:00（拘束655分・休憩60分）→ 勤務595分・残業115分（AttendanceCalculator：6時間超45分・8時間超60分を控除、残業は480分超））と、出勤のみ（退勤前）の行。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>山田 太郎の勤怠例（9:00〜18:00（拘束540分）に 12:00〜13:00 の休憩と 15:00〜15:10 の離席を打刻（attendance_breaks。KF-DD-TBL-10）→ work_minutes＝540−10−60＝470、残業 0／翌日 9:05〜20:00（拘束655分・休憩の打刻なし）→ 法定休憩60分を自動控除して勤務595分・残業115分（AttendanceCalculator：離席は常に控除、休憩は打刻があれば打刻分・無ければ 6時間超45分・8時間超60分を控除。残業は480分超））と、出勤のみ（退勤前）の行。
+例の INSERT は V1〜V5 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → attendance_breaks → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -5154,6 +5946,7 @@
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="10" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -5240,7 +6033,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>470</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -5335,6 +6128,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
@@ -5381,7 +6175,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO attendance_records(user_id,work_date,clock_in,clock_out,work_minutes,overtime_minutes) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),DATE '2026-10-01',TIMESTAMP '2026-10-01 09:00:00',TIMESTAMP '2026-10-01 18:00:00',480,0);</t>
+          <t>INSERT INTO attendance_records(user_id,work_date,clock_in,clock_out,work_minutes,overtime_minutes) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),DATE '2026-10-01',TIMESTAMP '2026-10-01 09:00:00',TIMESTAMP '2026-10-01 18:00:00',470,0);</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -5436,6 +6230,7 @@
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
@@ -5569,6 +6364,7 @@
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
